--- a/articles/43-does-this-decision-need-an-llm/templates/cost_per_acceptable_decision.xlsx
+++ b/articles/43-does-this-decision-need-an-llm/templates/cost_per_acceptable_decision.xlsx
@@ -1085,7 +1085,7 @@
     <row r="34">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>Prices are illustrative, not any provider's list price. See the article's technical appendix for dated provider prices.</t>
+          <t>Prices are illustrative, not any provider's list price. Check each provider's current pricing page.</t>
         </is>
       </c>
     </row>
